--- a/pipeline/credit_rating/output/xhtn_tong_hop_20261001.xlsx
+++ b/pipeline/credit_rating/output/xhtn_tong_hop_20261001.xlsx
@@ -681,7 +681,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -769,7 +769,7 @@
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:35</t>
+          <t>2026-10-01 15:39:59</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:19</t>
+          <t>2026-10-01 15:39:42</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -1753,7 +1753,7 @@
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -1875,7 +1875,7 @@
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -2297,7 +2297,7 @@
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -2381,7 +2381,7 @@
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
@@ -3633,7 +3633,7 @@
       <c r="AD29" t="inlineStr"/>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
@@ -3721,7 +3721,7 @@
       <c r="AD30" t="inlineStr"/>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:35</t>
+          <t>2026-10-01 15:39:59</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
@@ -4287,7 +4287,7 @@
       <c r="AD35" t="inlineStr"/>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:35</t>
+          <t>2026-10-01 15:39:59</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:35</t>
+          <t>2026-10-01 15:39:59</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
@@ -4513,7 +4513,7 @@
       <c r="AD37" t="inlineStr"/>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:35</t>
+          <t>2026-10-01 15:39:59</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:35</t>
+          <t>2026-10-01 15:39:59</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
@@ -5799,7 +5799,7 @@
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
@@ -6025,7 +6025,7 @@
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
@@ -6485,7 +6485,7 @@
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:35</t>
+          <t>2026-10-01 15:39:59</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF56" t="inlineStr">
@@ -6829,7 +6829,7 @@
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="AE58" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF58" t="inlineStr">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF59" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="AE60" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF60" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF61" t="inlineStr">
@@ -7369,7 +7369,7 @@
       </c>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
@@ -7479,7 +7479,7 @@
       </c>
       <c r="AE63" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF63" t="inlineStr">
@@ -7589,7 +7589,7 @@
       </c>
       <c r="AE64" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF64" t="inlineStr">
@@ -7705,7 +7705,7 @@
       </c>
       <c r="AE65" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF65" t="inlineStr">
@@ -7837,7 +7837,7 @@
       </c>
       <c r="AE66" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF66" t="inlineStr">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
@@ -8097,7 +8097,7 @@
       </c>
       <c r="AE68" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF68" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="AE69" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF69" t="inlineStr">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="AE70" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF70" t="inlineStr">
@@ -8447,7 +8447,7 @@
       </c>
       <c r="AE71" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF71" t="inlineStr">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="AE73" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF73" t="inlineStr">
@@ -8793,7 +8793,7 @@
       </c>
       <c r="AE74" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF74" t="inlineStr">
@@ -8893,7 +8893,7 @@
       </c>
       <c r="AE75" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF75" t="inlineStr">
@@ -9007,7 +9007,7 @@
       </c>
       <c r="AE76" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF76" t="inlineStr">
@@ -9123,7 +9123,7 @@
       </c>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:35</t>
+          <t>2026-10-01 15:39:59</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
@@ -9233,7 +9233,7 @@
       </c>
       <c r="AE78" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF78" t="inlineStr">
@@ -9347,7 +9347,7 @@
       </c>
       <c r="AE79" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF79" t="inlineStr">
@@ -9461,7 +9461,7 @@
       </c>
       <c r="AE80" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF80" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="AE81" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF81" t="inlineStr">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="AE82" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF82" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="AE83" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF83" t="inlineStr">
@@ -9911,7 +9911,7 @@
       </c>
       <c r="AE84" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF84" t="inlineStr">
@@ -10011,7 +10011,7 @@
       </c>
       <c r="AE85" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF85" t="inlineStr">
@@ -10125,7 +10125,7 @@
       </c>
       <c r="AE86" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF86" t="inlineStr">
@@ -10239,7 +10239,7 @@
       </c>
       <c r="AE87" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF87" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="AE88" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF88" t="inlineStr">
@@ -10453,7 +10453,7 @@
       </c>
       <c r="AE89" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:19</t>
+          <t>2026-10-01 15:39:42</t>
         </is>
       </c>
       <c r="AF89" t="inlineStr">
@@ -10563,7 +10563,7 @@
       </c>
       <c r="AE90" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF90" t="inlineStr">
@@ -10677,7 +10677,7 @@
       </c>
       <c r="AE91" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF91" t="inlineStr">
@@ -10791,7 +10791,7 @@
       </c>
       <c r="AE92" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF92" t="inlineStr">
@@ -10901,7 +10901,7 @@
       </c>
       <c r="AE93" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF93" t="inlineStr">
@@ -11015,7 +11015,7 @@
       </c>
       <c r="AE94" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF94" t="inlineStr">
@@ -11129,7 +11129,7 @@
       </c>
       <c r="AE95" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:19</t>
+          <t>2026-10-01 15:39:42</t>
         </is>
       </c>
       <c r="AF95" t="inlineStr">
@@ -11243,7 +11243,7 @@
       </c>
       <c r="AE96" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:19</t>
+          <t>2026-10-01 15:39:42</t>
         </is>
       </c>
       <c r="AF96" t="inlineStr">
@@ -11367,7 +11367,7 @@
       </c>
       <c r="AE97" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:22</t>
+          <t>2026-10-01 15:39:44</t>
         </is>
       </c>
       <c r="AF97" t="inlineStr">
@@ -11477,7 +11477,7 @@
       </c>
       <c r="AE98" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF98" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="AE99" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF99" t="inlineStr">
@@ -11705,7 +11705,7 @@
       </c>
       <c r="AE100" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF100" t="inlineStr">
@@ -11819,7 +11819,7 @@
       </c>
       <c r="AE101" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF101" t="inlineStr">
@@ -11931,7 +11931,7 @@
       </c>
       <c r="AE102" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF102" t="inlineStr">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="AE103" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:35</t>
+          <t>2026-10-01 15:39:59</t>
         </is>
       </c>
       <c r="AF103" t="inlineStr">
@@ -12157,7 +12157,7 @@
       </c>
       <c r="AE104" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF104" t="inlineStr">
@@ -12267,7 +12267,7 @@
       </c>
       <c r="AE105" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF105" t="inlineStr">
@@ -12385,7 +12385,7 @@
       </c>
       <c r="AE106" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:19</t>
+          <t>2026-10-01 15:39:42</t>
         </is>
       </c>
       <c r="AF106" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="AE107" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF107" t="inlineStr">
@@ -12629,7 +12629,7 @@
       </c>
       <c r="AE108" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF108" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="AE109" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF109" t="inlineStr">
@@ -12881,7 +12881,7 @@
       </c>
       <c r="AE110" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF110" t="inlineStr">
@@ -13005,7 +13005,7 @@
       </c>
       <c r="AE111" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF111" t="inlineStr">
@@ -13129,7 +13129,7 @@
       </c>
       <c r="AE112" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF112" t="inlineStr">
@@ -13229,7 +13229,7 @@
       </c>
       <c r="AE113" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF113" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="AE114" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF114" t="inlineStr">
@@ -13477,7 +13477,7 @@
       </c>
       <c r="AE115" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF115" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="AE116" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF116" t="inlineStr">
@@ -13705,7 +13705,7 @@
       </c>
       <c r="AE117" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF117" t="inlineStr">
@@ -13819,7 +13819,7 @@
       </c>
       <c r="AE118" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF118" t="inlineStr">
@@ -13929,7 +13929,7 @@
       </c>
       <c r="AE119" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF119" t="inlineStr">
@@ -14043,7 +14043,7 @@
       </c>
       <c r="AE120" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF120" t="inlineStr">
@@ -14157,7 +14157,7 @@
       </c>
       <c r="AE121" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF121" t="inlineStr">
@@ -14271,7 +14271,7 @@
       </c>
       <c r="AE122" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF122" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="AE123" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF123" t="inlineStr">
@@ -14505,7 +14505,7 @@
       </c>
       <c r="AE124" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF124" t="inlineStr">
@@ -14621,7 +14621,7 @@
       </c>
       <c r="AE125" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:35</t>
+          <t>2026-10-01 15:39:59</t>
         </is>
       </c>
       <c r="AF125" t="inlineStr">
@@ -14731,7 +14731,7 @@
       </c>
       <c r="AE126" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF126" t="inlineStr">
@@ -14851,7 +14851,7 @@
       </c>
       <c r="AE127" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF127" t="inlineStr">
@@ -14983,7 +14983,7 @@
       </c>
       <c r="AE128" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF128" t="inlineStr">
@@ -15111,7 +15111,7 @@
       </c>
       <c r="AE129" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF129" t="inlineStr">
@@ -15223,7 +15223,7 @@
       </c>
       <c r="AE130" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF130" t="inlineStr">
@@ -15333,7 +15333,7 @@
       </c>
       <c r="AE131" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF131" t="inlineStr">
@@ -15443,7 +15443,7 @@
       </c>
       <c r="AE132" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF132" t="inlineStr">
@@ -15553,7 +15553,7 @@
       </c>
       <c r="AE133" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF133" t="inlineStr">
@@ -15667,7 +15667,7 @@
       </c>
       <c r="AE134" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:19</t>
+          <t>2026-10-01 15:39:42</t>
         </is>
       </c>
       <c r="AF134" t="inlineStr">
@@ -15779,7 +15779,7 @@
       </c>
       <c r="AE135" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF135" t="inlineStr">
@@ -15895,7 +15895,7 @@
       </c>
       <c r="AE136" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF136" t="inlineStr">
@@ -16017,7 +16017,7 @@
       <c r="AD137" t="inlineStr"/>
       <c r="AE137" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF137" t="inlineStr">
@@ -16129,7 +16129,7 @@
       </c>
       <c r="AE138" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:22</t>
+          <t>2026-10-01 15:39:44</t>
         </is>
       </c>
       <c r="AF138" t="inlineStr">
@@ -16257,7 +16257,7 @@
       </c>
       <c r="AE139" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF139" t="inlineStr">
@@ -16377,7 +16377,7 @@
       </c>
       <c r="AE140" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF140" t="inlineStr">
@@ -16497,7 +16497,7 @@
       </c>
       <c r="AE141" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF141" t="inlineStr">
@@ -16607,7 +16607,7 @@
       </c>
       <c r="AE142" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF142" t="inlineStr">
@@ -16723,7 +16723,7 @@
       </c>
       <c r="AE143" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF143" t="inlineStr">
@@ -16835,7 +16835,7 @@
       </c>
       <c r="AE144" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF144" t="inlineStr">
@@ -16945,7 +16945,7 @@
       </c>
       <c r="AE145" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF145" t="inlineStr">
@@ -17055,7 +17055,7 @@
       </c>
       <c r="AE146" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF146" t="inlineStr">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="AE147" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF147" t="inlineStr">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="AE148" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF148" t="inlineStr">
@@ -17403,7 +17403,7 @@
       </c>
       <c r="AE149" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF149" t="inlineStr">
@@ -17515,7 +17515,7 @@
       </c>
       <c r="AE150" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF150" t="inlineStr">
@@ -17631,7 +17631,7 @@
       </c>
       <c r="AE151" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF151" t="inlineStr">
@@ -17741,7 +17741,7 @@
       </c>
       <c r="AE152" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF152" t="inlineStr">
@@ -17851,7 +17851,7 @@
       </c>
       <c r="AE153" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF153" t="inlineStr">
@@ -17971,7 +17971,7 @@
       </c>
       <c r="AE154" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF154" t="inlineStr">
@@ -18085,7 +18085,7 @@
       </c>
       <c r="AE155" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF155" t="inlineStr">
@@ -18199,7 +18199,7 @@
       </c>
       <c r="AE156" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF156" t="inlineStr">
@@ -18319,7 +18319,7 @@
       </c>
       <c r="AE157" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF157" t="inlineStr">
@@ -18429,7 +18429,7 @@
       </c>
       <c r="AE158" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF158" t="inlineStr">
@@ -18545,7 +18545,7 @@
       </c>
       <c r="AE159" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF159" t="inlineStr">
@@ -18657,7 +18657,7 @@
       </c>
       <c r="AE160" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:22</t>
+          <t>2026-10-01 15:39:44</t>
         </is>
       </c>
       <c r="AF160" t="inlineStr">
@@ -18769,7 +18769,7 @@
       </c>
       <c r="AE161" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF161" t="inlineStr">
@@ -18883,7 +18883,7 @@
       </c>
       <c r="AE162" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF162" t="inlineStr">
@@ -18997,7 +18997,7 @@
       </c>
       <c r="AE163" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF163" t="inlineStr">
@@ -19111,7 +19111,7 @@
       </c>
       <c r="AE164" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:19</t>
+          <t>2026-10-01 15:39:42</t>
         </is>
       </c>
       <c r="AF164" t="inlineStr">
@@ -19221,7 +19221,7 @@
       </c>
       <c r="AE165" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF165" t="inlineStr">
@@ -19331,7 +19331,7 @@
       </c>
       <c r="AE166" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF166" t="inlineStr">
@@ -19441,7 +19441,7 @@
       </c>
       <c r="AE167" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF167" t="inlineStr">
@@ -19555,7 +19555,7 @@
       </c>
       <c r="AE168" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF168" t="inlineStr">
@@ -19669,7 +19669,7 @@
       </c>
       <c r="AE169" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF169" t="inlineStr">
@@ -19797,7 +19797,7 @@
       </c>
       <c r="AE170" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF170" t="inlineStr">
@@ -19925,7 +19925,7 @@
       </c>
       <c r="AE171" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF171" t="inlineStr">
@@ -20035,7 +20035,7 @@
       </c>
       <c r="AE172" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF172" t="inlineStr">
@@ -20145,7 +20145,7 @@
       </c>
       <c r="AE173" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF173" t="inlineStr">
@@ -20265,7 +20265,7 @@
       </c>
       <c r="AE174" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF174" t="inlineStr">
@@ -20379,7 +20379,7 @@
       </c>
       <c r="AE175" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF175" t="inlineStr">
@@ -20489,7 +20489,7 @@
       </c>
       <c r="AE176" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF176" t="inlineStr">
@@ -20617,7 +20617,7 @@
       </c>
       <c r="AE177" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF177" t="inlineStr">
@@ -20739,7 +20739,7 @@
       <c r="AD178" t="inlineStr"/>
       <c r="AE178" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF178" t="inlineStr">
@@ -20867,7 +20867,7 @@
       </c>
       <c r="AE179" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF179" t="inlineStr">
@@ -20983,7 +20983,7 @@
       </c>
       <c r="AE180" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:35</t>
+          <t>2026-10-01 15:39:59</t>
         </is>
       </c>
       <c r="AF180" t="inlineStr">
@@ -21111,7 +21111,7 @@
       </c>
       <c r="AE181" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF181" t="inlineStr">
@@ -21243,7 +21243,7 @@
       </c>
       <c r="AE182" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF182" t="inlineStr">
@@ -21357,7 +21357,7 @@
       </c>
       <c r="AE183" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF183" t="inlineStr">
@@ -21479,7 +21479,7 @@
       <c r="AD184" t="inlineStr"/>
       <c r="AE184" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF184" t="inlineStr">
@@ -21591,7 +21591,7 @@
       </c>
       <c r="AE185" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF185" t="inlineStr">
@@ -21691,7 +21691,7 @@
       </c>
       <c r="AE186" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF186" t="inlineStr">
@@ -21801,7 +21801,7 @@
       </c>
       <c r="AE187" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF187" t="inlineStr">
@@ -21917,7 +21917,7 @@
       </c>
       <c r="AE188" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF188" t="inlineStr">
@@ -22033,7 +22033,7 @@
       </c>
       <c r="AE189" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF189" t="inlineStr">
@@ -22161,7 +22161,7 @@
       </c>
       <c r="AE190" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF190" t="inlineStr">
@@ -22271,7 +22271,7 @@
       </c>
       <c r="AE191" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF191" t="inlineStr">
@@ -22385,7 +22385,7 @@
       </c>
       <c r="AE192" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF192" t="inlineStr">
@@ -22499,7 +22499,7 @@
       </c>
       <c r="AE193" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF193" t="inlineStr">
@@ -22613,7 +22613,7 @@
       </c>
       <c r="AE194" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF194" t="inlineStr">
@@ -22723,7 +22723,7 @@
       </c>
       <c r="AE195" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF195" t="inlineStr">
@@ -22837,7 +22837,7 @@
       </c>
       <c r="AE196" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF196" t="inlineStr">
@@ -22947,7 +22947,7 @@
       </c>
       <c r="AE197" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF197" t="inlineStr">
@@ -23059,7 +23059,7 @@
       </c>
       <c r="AE198" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF198" t="inlineStr">
@@ -23175,7 +23175,7 @@
       </c>
       <c r="AE199" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:35</t>
+          <t>2026-10-01 15:39:59</t>
         </is>
       </c>
       <c r="AF199" t="inlineStr">
@@ -23291,7 +23291,7 @@
       </c>
       <c r="AE200" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF200" t="inlineStr">
@@ -23403,7 +23403,7 @@
       </c>
       <c r="AE201" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF201" t="inlineStr">
@@ -23515,7 +23515,7 @@
       </c>
       <c r="AE202" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF202" t="inlineStr">
@@ -23627,7 +23627,7 @@
       </c>
       <c r="AE203" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF203" t="inlineStr">
@@ -23755,7 +23755,7 @@
       </c>
       <c r="AE204" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:22</t>
+          <t>2026-10-01 15:39:44</t>
         </is>
       </c>
       <c r="AF204" t="inlineStr">
@@ -23865,7 +23865,7 @@
       </c>
       <c r="AE205" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF205" t="inlineStr">
@@ -23985,7 +23985,7 @@
       </c>
       <c r="AE206" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF206" t="inlineStr">
@@ -24107,7 +24107,7 @@
       <c r="AD207" t="inlineStr"/>
       <c r="AE207" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF207" t="inlineStr">
@@ -24233,7 +24233,7 @@
       <c r="AD208" t="inlineStr"/>
       <c r="AE208" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF208" t="inlineStr">
@@ -24359,7 +24359,7 @@
       <c r="AD209" t="inlineStr"/>
       <c r="AE209" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF209" t="inlineStr">
@@ -24475,7 +24475,7 @@
       </c>
       <c r="AE210" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:35</t>
+          <t>2026-10-01 15:39:59</t>
         </is>
       </c>
       <c r="AF210" t="inlineStr">
@@ -24589,7 +24589,7 @@
       </c>
       <c r="AE211" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF211" t="inlineStr">
@@ -24703,7 +24703,7 @@
       </c>
       <c r="AE212" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF212" t="inlineStr">
@@ -24817,7 +24817,7 @@
       </c>
       <c r="AE213" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF213" t="inlineStr">
@@ -24937,7 +24937,7 @@
       </c>
       <c r="AE214" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF214" t="inlineStr">
@@ -25057,7 +25057,7 @@
       </c>
       <c r="AE215" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF215" t="inlineStr">
@@ -25167,7 +25167,7 @@
       </c>
       <c r="AE216" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF216" t="inlineStr">
@@ -25277,7 +25277,7 @@
       </c>
       <c r="AE217" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF217" t="inlineStr">
@@ -25387,7 +25387,7 @@
       </c>
       <c r="AE218" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF218" t="inlineStr">
@@ -25503,7 +25503,7 @@
       </c>
       <c r="AE219" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF219" t="inlineStr">
@@ -25631,7 +25631,7 @@
       </c>
       <c r="AE220" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF220" t="inlineStr">
@@ -25743,7 +25743,7 @@
       </c>
       <c r="AE221" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF221" t="inlineStr">
@@ -25855,7 +25855,7 @@
       </c>
       <c r="AE222" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF222" t="inlineStr">
@@ -25973,7 +25973,7 @@
       </c>
       <c r="AE223" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:19</t>
+          <t>2026-10-01 15:39:42</t>
         </is>
       </c>
       <c r="AF223" t="inlineStr">
@@ -26083,7 +26083,7 @@
       </c>
       <c r="AE224" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF224" t="inlineStr">
@@ -26193,7 +26193,7 @@
       </c>
       <c r="AE225" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF225" t="inlineStr">
@@ -26305,7 +26305,7 @@
       </c>
       <c r="AE226" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF226" t="inlineStr">
@@ -26415,7 +26415,7 @@
       </c>
       <c r="AE227" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF227" t="inlineStr">
@@ -26535,7 +26535,7 @@
       </c>
       <c r="AE228" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF228" t="inlineStr">
@@ -26651,7 +26651,7 @@
       </c>
       <c r="AE229" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF229" t="inlineStr">
@@ -26767,7 +26767,7 @@
       </c>
       <c r="AE230" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF230" t="inlineStr">
@@ -26895,7 +26895,7 @@
       </c>
       <c r="AE231" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF231" t="inlineStr">
@@ -27007,7 +27007,7 @@
       </c>
       <c r="AE232" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF232" t="inlineStr">
@@ -27119,7 +27119,7 @@
       </c>
       <c r="AE233" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF233" t="inlineStr">
@@ -27231,7 +27231,7 @@
       </c>
       <c r="AE234" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF234" t="inlineStr">
@@ -27347,7 +27347,7 @@
       </c>
       <c r="AE235" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF235" t="inlineStr">
@@ -27457,7 +27457,7 @@
       </c>
       <c r="AE236" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF236" t="inlineStr">
@@ -27577,7 +27577,7 @@
       </c>
       <c r="AE237" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF237" t="inlineStr">
@@ -27687,7 +27687,7 @@
       </c>
       <c r="AE238" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF238" t="inlineStr">
@@ -27807,7 +27807,7 @@
       </c>
       <c r="AE239" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF239" t="inlineStr">
@@ -27917,7 +27917,7 @@
       </c>
       <c r="AE240" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF240" t="inlineStr">
@@ -28031,7 +28031,7 @@
       </c>
       <c r="AE241" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:19</t>
+          <t>2026-10-01 15:39:42</t>
         </is>
       </c>
       <c r="AF241" t="inlineStr">
@@ -28141,7 +28141,7 @@
       </c>
       <c r="AE242" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF242" t="inlineStr">
@@ -28251,7 +28251,7 @@
       </c>
       <c r="AE243" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF243" t="inlineStr">
@@ -28365,7 +28365,7 @@
       </c>
       <c r="AE244" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF244" t="inlineStr">
@@ -28475,7 +28475,7 @@
       </c>
       <c r="AE245" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF245" t="inlineStr">
@@ -28587,7 +28587,7 @@
       </c>
       <c r="AE246" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF246" t="inlineStr">
@@ -28697,7 +28697,7 @@
       </c>
       <c r="AE247" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF247" t="inlineStr">
@@ -28817,7 +28817,7 @@
       </c>
       <c r="AE248" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF248" t="inlineStr">
@@ -28929,7 +28929,7 @@
       </c>
       <c r="AE249" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF249" t="inlineStr">
@@ -29039,7 +29039,7 @@
       </c>
       <c r="AE250" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF250" t="inlineStr">
@@ -29163,7 +29163,7 @@
       </c>
       <c r="AE251" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:22</t>
+          <t>2026-10-01 15:39:44</t>
         </is>
       </c>
       <c r="AF251" t="inlineStr">
@@ -29287,7 +29287,7 @@
       </c>
       <c r="AE252" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:22</t>
+          <t>2026-10-01 15:39:44</t>
         </is>
       </c>
       <c r="AF252" t="inlineStr">
@@ -29397,7 +29397,7 @@
       </c>
       <c r="AE253" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF253" t="inlineStr">
@@ -29507,7 +29507,7 @@
       </c>
       <c r="AE254" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF254" t="inlineStr">
@@ -29617,7 +29617,7 @@
       </c>
       <c r="AE255" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF255" t="inlineStr">
@@ -29729,7 +29729,7 @@
       </c>
       <c r="AE256" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF256" t="inlineStr">
@@ -29839,7 +29839,7 @@
       </c>
       <c r="AE257" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF257" t="inlineStr">
@@ -29949,7 +29949,7 @@
       </c>
       <c r="AE258" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF258" t="inlineStr">
@@ -30077,7 +30077,7 @@
       </c>
       <c r="AE259" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF259" t="inlineStr">
@@ -30183,7 +30183,7 @@
       </c>
       <c r="AE260" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF260" t="inlineStr">
@@ -30295,7 +30295,7 @@
       </c>
       <c r="AE261" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF261" t="inlineStr">
@@ -30411,7 +30411,7 @@
       </c>
       <c r="AE262" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:35</t>
+          <t>2026-10-01 15:39:59</t>
         </is>
       </c>
       <c r="AF262" t="inlineStr">
@@ -30527,7 +30527,7 @@
       </c>
       <c r="AE263" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:35</t>
+          <t>2026-10-01 15:39:59</t>
         </is>
       </c>
       <c r="AF263" t="inlineStr">
@@ -30637,7 +30637,7 @@
       </c>
       <c r="AE264" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF264" t="inlineStr">
@@ -30747,7 +30747,7 @@
       </c>
       <c r="AE265" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF265" t="inlineStr">
@@ -30863,7 +30863,7 @@
       </c>
       <c r="AE266" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:35</t>
+          <t>2026-10-01 15:39:59</t>
         </is>
       </c>
       <c r="AF266" t="inlineStr">
@@ -30979,7 +30979,7 @@
       </c>
       <c r="AE267" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:35</t>
+          <t>2026-10-01 15:39:59</t>
         </is>
       </c>
       <c r="AF267" t="inlineStr">
@@ -31089,7 +31089,7 @@
       </c>
       <c r="AE268" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF268" t="inlineStr">
@@ -31205,7 +31205,7 @@
       </c>
       <c r="AE269" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:35</t>
+          <t>2026-10-01 15:39:59</t>
         </is>
       </c>
       <c r="AF269" t="inlineStr">
@@ -31321,7 +31321,7 @@
       </c>
       <c r="AE270" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:35</t>
+          <t>2026-10-01 15:39:59</t>
         </is>
       </c>
       <c r="AF270" t="inlineStr">
@@ -31431,7 +31431,7 @@
       </c>
       <c r="AE271" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF271" t="inlineStr">
@@ -31541,7 +31541,7 @@
       </c>
       <c r="AE272" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF272" t="inlineStr">
@@ -31651,7 +31651,7 @@
       </c>
       <c r="AE273" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF273" t="inlineStr">
@@ -31751,7 +31751,7 @@
       </c>
       <c r="AE274" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF274" t="inlineStr">
@@ -31861,7 +31861,7 @@
       </c>
       <c r="AE275" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF275" t="inlineStr">
@@ -31973,7 +31973,7 @@
       </c>
       <c r="AE276" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF276" t="inlineStr">
@@ -32083,7 +32083,7 @@
       </c>
       <c r="AE277" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF277" t="inlineStr">
@@ -32203,7 +32203,7 @@
       </c>
       <c r="AE278" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF278" t="inlineStr">
@@ -32315,7 +32315,7 @@
       </c>
       <c r="AE279" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF279" t="inlineStr">
@@ -32425,7 +32425,7 @@
       </c>
       <c r="AE280" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF280" t="inlineStr">
@@ -32537,7 +32537,7 @@
       </c>
       <c r="AE281" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF281" t="inlineStr">
@@ -32653,7 +32653,7 @@
       </c>
       <c r="AE282" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF282" t="inlineStr">
@@ -32765,7 +32765,7 @@
       </c>
       <c r="AE283" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF283" t="inlineStr">
@@ -32875,7 +32875,7 @@
       </c>
       <c r="AE284" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF284" t="inlineStr">
@@ -32991,7 +32991,7 @@
       </c>
       <c r="AE285" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF285" t="inlineStr">
@@ -33101,7 +33101,7 @@
       </c>
       <c r="AE286" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF286" t="inlineStr">
@@ -33227,7 +33227,7 @@
       <c r="AD287" t="inlineStr"/>
       <c r="AE287" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF287" t="inlineStr">
@@ -33355,7 +33355,7 @@
       </c>
       <c r="AE288" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF288" t="inlineStr">
@@ -33467,7 +33467,7 @@
       </c>
       <c r="AE289" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF289" t="inlineStr">
@@ -33567,7 +33567,7 @@
       </c>
       <c r="AE290" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF290" t="inlineStr">
@@ -33667,7 +33667,7 @@
       </c>
       <c r="AE291" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF291" t="inlineStr">
@@ -33781,7 +33781,7 @@
       </c>
       <c r="AE292" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF292" t="inlineStr">
@@ -33895,7 +33895,7 @@
       </c>
       <c r="AE293" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF293" t="inlineStr">
@@ -33995,7 +33995,7 @@
       </c>
       <c r="AE294" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF294" t="inlineStr">
@@ -34115,7 +34115,7 @@
       </c>
       <c r="AE295" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF295" t="inlineStr">
@@ -34227,7 +34227,7 @@
       </c>
       <c r="AE296" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF296" t="inlineStr">
@@ -34339,7 +34339,7 @@
       </c>
       <c r="AE297" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF297" t="inlineStr">
@@ -34453,7 +34453,7 @@
       </c>
       <c r="AE298" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF298" t="inlineStr">
@@ -34567,7 +34567,7 @@
       </c>
       <c r="AE299" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:19</t>
+          <t>2026-10-01 15:39:42</t>
         </is>
       </c>
       <c r="AF299" t="inlineStr">
@@ -34681,7 +34681,7 @@
       </c>
       <c r="AE300" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:19</t>
+          <t>2026-10-01 15:39:42</t>
         </is>
       </c>
       <c r="AF300" t="inlineStr">
@@ -34813,7 +34813,7 @@
       </c>
       <c r="AE301" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF301" t="inlineStr">
@@ -34941,7 +34941,7 @@
       </c>
       <c r="AE302" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF302" t="inlineStr">
@@ -35069,7 +35069,7 @@
       </c>
       <c r="AE303" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF303" t="inlineStr">
@@ -35197,7 +35197,7 @@
       </c>
       <c r="AE304" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF304" t="inlineStr">
@@ -35309,7 +35309,7 @@
       </c>
       <c r="AE305" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF305" t="inlineStr">
@@ -35421,7 +35421,7 @@
       </c>
       <c r="AE306" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF306" t="inlineStr">
@@ -35531,7 +35531,7 @@
       </c>
       <c r="AE307" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF307" t="inlineStr">
@@ -35641,7 +35641,7 @@
       </c>
       <c r="AE308" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF308" t="inlineStr">
@@ -35769,7 +35769,7 @@
       </c>
       <c r="AE309" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF309" t="inlineStr">
@@ -35879,7 +35879,7 @@
       </c>
       <c r="AE310" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF310" t="inlineStr">
@@ -36007,7 +36007,7 @@
       </c>
       <c r="AE311" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF311" t="inlineStr">
@@ -36119,7 +36119,7 @@
       </c>
       <c r="AE312" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF312" t="inlineStr">
@@ -36231,7 +36231,7 @@
       </c>
       <c r="AE313" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF313" t="inlineStr">
@@ -36341,7 +36341,7 @@
       </c>
       <c r="AE314" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF314" t="inlineStr">
@@ -36461,7 +36461,7 @@
       </c>
       <c r="AE315" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF315" t="inlineStr">
@@ -36585,7 +36585,7 @@
       </c>
       <c r="AE316" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF316" t="inlineStr">
@@ -36709,7 +36709,7 @@
       </c>
       <c r="AE317" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF317" t="inlineStr">
@@ -36833,7 +36833,7 @@
       </c>
       <c r="AE318" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF318" t="inlineStr">
@@ -36945,7 +36945,7 @@
       </c>
       <c r="AE319" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF319" t="inlineStr">
@@ -37061,7 +37061,7 @@
       </c>
       <c r="AE320" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF320" t="inlineStr">
@@ -37173,7 +37173,7 @@
       </c>
       <c r="AE321" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:22</t>
+          <t>2026-10-01 15:39:44</t>
         </is>
       </c>
       <c r="AF321" t="inlineStr">
@@ -37301,7 +37301,7 @@
       </c>
       <c r="AE322" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:22</t>
+          <t>2026-10-01 15:39:44</t>
         </is>
       </c>
       <c r="AF322" t="inlineStr">
@@ -37429,7 +37429,7 @@
       </c>
       <c r="AE323" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF323" t="inlineStr">
@@ -37541,7 +37541,7 @@
       </c>
       <c r="AE324" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF324" t="inlineStr">
@@ -37653,7 +37653,7 @@
       </c>
       <c r="AE325" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF325" t="inlineStr">
@@ -37763,7 +37763,7 @@
       </c>
       <c r="AE326" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF326" t="inlineStr">
@@ -37873,7 +37873,7 @@
       </c>
       <c r="AE327" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF327" t="inlineStr">
@@ -37989,7 +37989,7 @@
       </c>
       <c r="AE328" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF328" t="inlineStr">
@@ -38101,7 +38101,7 @@
       </c>
       <c r="AE329" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF329" t="inlineStr">
@@ -38221,7 +38221,7 @@
       </c>
       <c r="AE330" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF330" t="inlineStr">
@@ -38349,7 +38349,7 @@
       </c>
       <c r="AE331" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF331" t="inlineStr">
@@ -38465,7 +38465,7 @@
       </c>
       <c r="AE332" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF332" t="inlineStr">
@@ -38565,7 +38565,7 @@
       </c>
       <c r="AE333" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF333" t="inlineStr">
@@ -38677,7 +38677,7 @@
       </c>
       <c r="AE334" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF334" t="inlineStr">
@@ -38805,7 +38805,7 @@
       </c>
       <c r="AE335" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF335" t="inlineStr">
@@ -38929,7 +38929,7 @@
       </c>
       <c r="AE336" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:22</t>
+          <t>2026-10-01 15:39:44</t>
         </is>
       </c>
       <c r="AF336" t="inlineStr">
@@ -39041,7 +39041,7 @@
       </c>
       <c r="AE337" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF337" t="inlineStr">
@@ -39151,7 +39151,7 @@
       </c>
       <c r="AE338" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF338" t="inlineStr">
@@ -39261,7 +39261,7 @@
       </c>
       <c r="AE339" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF339" t="inlineStr">
@@ -39371,7 +39371,7 @@
       </c>
       <c r="AE340" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF340" t="inlineStr">
@@ -39481,7 +39481,7 @@
       </c>
       <c r="AE341" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF341" t="inlineStr">
@@ -39601,7 +39601,7 @@
       </c>
       <c r="AE342" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF342" t="inlineStr">
@@ -39711,7 +39711,7 @@
       </c>
       <c r="AE343" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF343" t="inlineStr">
@@ -39821,7 +39821,7 @@
       </c>
       <c r="AE344" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF344" t="inlineStr">
@@ -39931,7 +39931,7 @@
       </c>
       <c r="AE345" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF345" t="inlineStr">
@@ -40051,7 +40051,7 @@
       </c>
       <c r="AE346" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF346" t="inlineStr">
@@ -40171,7 +40171,7 @@
       </c>
       <c r="AE347" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF347" t="inlineStr">
@@ -40291,7 +40291,7 @@
       </c>
       <c r="AE348" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF348" t="inlineStr">
@@ -40411,7 +40411,7 @@
       </c>
       <c r="AE349" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF349" t="inlineStr">
@@ -40527,7 +40527,7 @@
       </c>
       <c r="AE350" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:35</t>
+          <t>2026-10-01 15:39:59</t>
         </is>
       </c>
       <c r="AF350" t="inlineStr">
@@ -40643,7 +40643,7 @@
       </c>
       <c r="AE351" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:35</t>
+          <t>2026-10-01 15:39:59</t>
         </is>
       </c>
       <c r="AF351" t="inlineStr">
@@ -40759,7 +40759,7 @@
       </c>
       <c r="AE352" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:35</t>
+          <t>2026-10-01 15:39:59</t>
         </is>
       </c>
       <c r="AF352" t="inlineStr">
@@ -40871,7 +40871,7 @@
       </c>
       <c r="AE353" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF353" t="inlineStr">
@@ -40987,7 +40987,7 @@
       </c>
       <c r="AE354" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:35</t>
+          <t>2026-10-01 15:39:59</t>
         </is>
       </c>
       <c r="AF354" t="inlineStr">
@@ -41107,7 +41107,7 @@
       </c>
       <c r="AE355" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF355" t="inlineStr">
@@ -41219,7 +41219,7 @@
       </c>
       <c r="AE356" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF356" t="inlineStr">
@@ -41335,7 +41335,7 @@
       </c>
       <c r="AE357" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:35</t>
+          <t>2026-10-01 15:39:59</t>
         </is>
       </c>
       <c r="AF357" t="inlineStr">
@@ -41451,7 +41451,7 @@
       </c>
       <c r="AE358" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:35</t>
+          <t>2026-10-01 15:39:59</t>
         </is>
       </c>
       <c r="AF358" t="inlineStr">
@@ -41567,7 +41567,7 @@
       </c>
       <c r="AE359" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:35</t>
+          <t>2026-10-01 15:39:59</t>
         </is>
       </c>
       <c r="AF359" t="inlineStr">
@@ -41683,7 +41683,7 @@
       </c>
       <c r="AE360" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:35</t>
+          <t>2026-10-01 15:39:59</t>
         </is>
       </c>
       <c r="AF360" t="inlineStr">
@@ -41797,7 +41797,7 @@
       </c>
       <c r="AE361" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:19</t>
+          <t>2026-10-01 15:39:42</t>
         </is>
       </c>
       <c r="AF361" t="inlineStr">
@@ -41913,7 +41913,7 @@
       </c>
       <c r="AE362" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:35</t>
+          <t>2026-10-01 15:39:59</t>
         </is>
       </c>
       <c r="AF362" t="inlineStr">
@@ -42029,7 +42029,7 @@
       </c>
       <c r="AE363" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:35</t>
+          <t>2026-10-01 15:39:59</t>
         </is>
       </c>
       <c r="AF363" t="inlineStr">
@@ -42145,7 +42145,7 @@
       </c>
       <c r="AE364" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:35</t>
+          <t>2026-10-01 15:39:59</t>
         </is>
       </c>
       <c r="AF364" t="inlineStr">
@@ -42255,7 +42255,7 @@
       </c>
       <c r="AE365" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF365" t="inlineStr">
@@ -42371,7 +42371,7 @@
       </c>
       <c r="AE366" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF366" t="inlineStr">
@@ -42483,7 +42483,7 @@
       </c>
       <c r="AE367" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF367" t="inlineStr">
@@ -42593,7 +42593,7 @@
       </c>
       <c r="AE368" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF368" t="inlineStr">
@@ -42705,7 +42705,7 @@
       </c>
       <c r="AE369" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF369" t="inlineStr">
@@ -42817,7 +42817,7 @@
       </c>
       <c r="AE370" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF370" t="inlineStr">
@@ -42929,7 +42929,7 @@
       </c>
       <c r="AE371" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF371" t="inlineStr">
@@ -43049,7 +43049,7 @@
       </c>
       <c r="AE372" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF372" t="inlineStr">
@@ -43177,7 +43177,7 @@
       </c>
       <c r="AE373" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF373" t="inlineStr">
@@ -43297,7 +43297,7 @@
       </c>
       <c r="AE374" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF374" t="inlineStr">
@@ -43425,7 +43425,7 @@
       </c>
       <c r="AE375" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF375" t="inlineStr">
@@ -43537,7 +43537,7 @@
       </c>
       <c r="AE376" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF376" t="inlineStr">
@@ -43647,7 +43647,7 @@
       </c>
       <c r="AE377" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF377" t="inlineStr">
@@ -43757,7 +43757,7 @@
       </c>
       <c r="AE378" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF378" t="inlineStr">
@@ -43869,7 +43869,7 @@
       </c>
       <c r="AE379" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF379" t="inlineStr">
@@ -43981,7 +43981,7 @@
       </c>
       <c r="AE380" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF380" t="inlineStr">
@@ -44091,7 +44091,7 @@
       </c>
       <c r="AE381" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF381" t="inlineStr">
@@ -44207,7 +44207,7 @@
       </c>
       <c r="AE382" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF382" t="inlineStr">
@@ -44317,7 +44317,7 @@
       </c>
       <c r="AE383" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF383" t="inlineStr">
@@ -44429,7 +44429,7 @@
       </c>
       <c r="AE384" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF384" t="inlineStr">
@@ -44539,7 +44539,7 @@
       </c>
       <c r="AE385" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF385" t="inlineStr">
@@ -44649,7 +44649,7 @@
       </c>
       <c r="AE386" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF386" t="inlineStr">
@@ -44777,7 +44777,7 @@
       </c>
       <c r="AE387" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF387" t="inlineStr">
@@ -44889,7 +44889,7 @@
       </c>
       <c r="AE388" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF388" t="inlineStr">
@@ -45017,7 +45017,7 @@
       </c>
       <c r="AE389" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF389" t="inlineStr">
@@ -45129,7 +45129,7 @@
       </c>
       <c r="AE390" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF390" t="inlineStr">
@@ -45239,7 +45239,7 @@
       </c>
       <c r="AE391" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF391" t="inlineStr">
@@ -45349,7 +45349,7 @@
       </c>
       <c r="AE392" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF392" t="inlineStr">
@@ -45459,7 +45459,7 @@
       </c>
       <c r="AE393" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF393" t="inlineStr">
@@ -45571,7 +45571,7 @@
       </c>
       <c r="AE394" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF394" t="inlineStr">
@@ -45681,7 +45681,7 @@
       </c>
       <c r="AE395" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF395" t="inlineStr">
@@ -45809,7 +45809,7 @@
       </c>
       <c r="AE396" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF396" t="inlineStr">
@@ -45921,7 +45921,7 @@
       </c>
       <c r="AE397" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF397" t="inlineStr">
@@ -46031,7 +46031,7 @@
       </c>
       <c r="AE398" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF398" t="inlineStr">
@@ -46141,7 +46141,7 @@
       </c>
       <c r="AE399" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF399" t="inlineStr">
@@ -46251,7 +46251,7 @@
       </c>
       <c r="AE400" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF400" t="inlineStr">
@@ -46361,7 +46361,7 @@
       </c>
       <c r="AE401" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF401" t="inlineStr">
@@ -46471,7 +46471,7 @@
       </c>
       <c r="AE402" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF402" t="inlineStr">
@@ -46583,7 +46583,7 @@
       </c>
       <c r="AE403" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF403" t="inlineStr">
@@ -46711,7 +46711,7 @@
       </c>
       <c r="AE404" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF404" t="inlineStr">
@@ -46821,7 +46821,7 @@
       </c>
       <c r="AE405" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF405" t="inlineStr">
@@ -46931,7 +46931,7 @@
       </c>
       <c r="AE406" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF406" t="inlineStr">
@@ -47043,7 +47043,7 @@
       </c>
       <c r="AE407" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:22</t>
+          <t>2026-10-01 15:39:44</t>
         </is>
       </c>
       <c r="AF407" t="inlineStr">
@@ -47153,7 +47153,7 @@
       </c>
       <c r="AE408" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF408" t="inlineStr">
@@ -47265,7 +47265,7 @@
       </c>
       <c r="AE409" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF409" t="inlineStr">
@@ -47393,7 +47393,7 @@
       </c>
       <c r="AE410" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF410" t="inlineStr">
@@ -47503,7 +47503,7 @@
       </c>
       <c r="AE411" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF411" t="inlineStr">
@@ -47615,7 +47615,7 @@
       </c>
       <c r="AE412" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF412" t="inlineStr">
@@ -47725,7 +47725,7 @@
       </c>
       <c r="AE413" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF413" t="inlineStr">
@@ -47835,7 +47835,7 @@
       </c>
       <c r="AE414" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF414" t="inlineStr">
@@ -47945,7 +47945,7 @@
       </c>
       <c r="AE415" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF415" t="inlineStr">
@@ -48045,7 +48045,7 @@
       </c>
       <c r="AE416" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF416" t="inlineStr">
@@ -48155,7 +48155,7 @@
       </c>
       <c r="AE417" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF417" t="inlineStr">
@@ -48255,7 +48255,7 @@
       </c>
       <c r="AE418" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF418" t="inlineStr">
@@ -48365,7 +48365,7 @@
       </c>
       <c r="AE419" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF419" t="inlineStr">
@@ -48493,7 +48493,7 @@
       </c>
       <c r="AE420" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF420" t="inlineStr">
@@ -48603,7 +48603,7 @@
       </c>
       <c r="AE421" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF421" t="inlineStr">
@@ -48713,7 +48713,7 @@
       </c>
       <c r="AE422" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF422" t="inlineStr">
@@ -48823,7 +48823,7 @@
       </c>
       <c r="AE423" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF423" t="inlineStr">
@@ -48933,7 +48933,7 @@
       </c>
       <c r="AE424" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF424" t="inlineStr">
@@ -49043,7 +49043,7 @@
       </c>
       <c r="AE425" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF425" t="inlineStr">
@@ -49153,7 +49153,7 @@
       </c>
       <c r="AE426" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF426" t="inlineStr">
@@ -49263,7 +49263,7 @@
       </c>
       <c r="AE427" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF427" t="inlineStr">
@@ -49373,7 +49373,7 @@
       </c>
       <c r="AE428" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF428" t="inlineStr">
@@ -49501,7 +49501,7 @@
       </c>
       <c r="AE429" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF429" t="inlineStr">
@@ -49613,7 +49613,7 @@
       </c>
       <c r="AE430" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF430" t="inlineStr">
@@ -49713,7 +49713,7 @@
       </c>
       <c r="AE431" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF431" t="inlineStr">
@@ -49823,7 +49823,7 @@
       </c>
       <c r="AE432" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF432" t="inlineStr">
@@ -49937,7 +49937,7 @@
       </c>
       <c r="AE433" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF433" t="inlineStr">
@@ -50047,7 +50047,7 @@
       </c>
       <c r="AE434" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF434" t="inlineStr">
@@ -50147,7 +50147,7 @@
       </c>
       <c r="AE435" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF435" t="inlineStr">
@@ -50259,7 +50259,7 @@
       </c>
       <c r="AE436" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF436" t="inlineStr">
@@ -50371,7 +50371,7 @@
       </c>
       <c r="AE437" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF437" t="inlineStr">
@@ -50481,7 +50481,7 @@
       </c>
       <c r="AE438" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF438" t="inlineStr">
@@ -50593,7 +50593,7 @@
       </c>
       <c r="AE439" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF439" t="inlineStr">
@@ -50705,7 +50705,7 @@
       </c>
       <c r="AE440" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF440" t="inlineStr">
@@ -50815,7 +50815,7 @@
       </c>
       <c r="AE441" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF441" t="inlineStr">
@@ -50943,7 +50943,7 @@
       </c>
       <c r="AE442" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF442" t="inlineStr">
@@ -51075,7 +51075,7 @@
       </c>
       <c r="AE443" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF443" t="inlineStr">
@@ -51207,7 +51207,7 @@
       </c>
       <c r="AE444" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF444" t="inlineStr">
@@ -51339,7 +51339,7 @@
       </c>
       <c r="AE445" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF445" t="inlineStr">
@@ -51463,7 +51463,7 @@
       </c>
       <c r="AE446" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:22</t>
+          <t>2026-10-01 15:39:44</t>
         </is>
       </c>
       <c r="AF446" t="inlineStr">
@@ -51575,7 +51575,7 @@
       </c>
       <c r="AE447" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF447" t="inlineStr">
@@ -51675,7 +51675,7 @@
       </c>
       <c r="AE448" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF448" t="inlineStr">
@@ -51795,7 +51795,7 @@
       </c>
       <c r="AE449" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF449" t="inlineStr">
@@ -51911,7 +51911,7 @@
       </c>
       <c r="AE450" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF450" t="inlineStr">
@@ -52023,7 +52023,7 @@
       </c>
       <c r="AE451" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF451" t="inlineStr">
@@ -52145,7 +52145,7 @@
       <c r="AD452" t="inlineStr"/>
       <c r="AE452" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF452" t="inlineStr">
@@ -52257,7 +52257,7 @@
       </c>
       <c r="AE453" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF453" t="inlineStr">
@@ -52367,7 +52367,7 @@
       </c>
       <c r="AE454" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF454" t="inlineStr">
@@ -52477,7 +52477,7 @@
       </c>
       <c r="AE455" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF455" t="inlineStr">
@@ -52587,7 +52587,7 @@
       </c>
       <c r="AE456" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF456" t="inlineStr">
@@ -52697,7 +52697,7 @@
       </c>
       <c r="AE457" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF457" t="inlineStr">
@@ -52825,7 +52825,7 @@
       </c>
       <c r="AE458" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF458" t="inlineStr">
@@ -52941,7 +52941,7 @@
       </c>
       <c r="AE459" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF459" t="inlineStr">
@@ -53051,7 +53051,7 @@
       </c>
       <c r="AE460" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF460" t="inlineStr">
@@ -53179,7 +53179,7 @@
       </c>
       <c r="AE461" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF461" t="inlineStr">
@@ -53307,7 +53307,7 @@
       </c>
       <c r="AE462" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF462" t="inlineStr">
@@ -53435,7 +53435,7 @@
       </c>
       <c r="AE463" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF463" t="inlineStr">
@@ -53563,7 +53563,7 @@
       </c>
       <c r="AE464" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF464" t="inlineStr">
@@ -53675,7 +53675,7 @@
       </c>
       <c r="AE465" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF465" t="inlineStr">
@@ -53785,7 +53785,7 @@
       </c>
       <c r="AE466" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF466" t="inlineStr">
@@ -53913,7 +53913,7 @@
       </c>
       <c r="AE467" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF467" t="inlineStr">
@@ -54025,7 +54025,7 @@
       </c>
       <c r="AE468" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF468" t="inlineStr">
@@ -54137,7 +54137,7 @@
       </c>
       <c r="AE469" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF469" t="inlineStr">
@@ -54253,7 +54253,7 @@
       </c>
       <c r="AE470" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF470" t="inlineStr">
@@ -54365,7 +54365,7 @@
       </c>
       <c r="AE471" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF471" t="inlineStr">
@@ -54477,7 +54477,7 @@
       </c>
       <c r="AE472" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF472" t="inlineStr">
@@ -54589,7 +54589,7 @@
       </c>
       <c r="AE473" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF473" t="inlineStr">
@@ -54701,7 +54701,7 @@
       </c>
       <c r="AE474" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF474" t="inlineStr">
@@ -54821,7 +54821,7 @@
       </c>
       <c r="AE475" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF475" t="inlineStr">
@@ -54931,7 +54931,7 @@
       </c>
       <c r="AE476" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF476" t="inlineStr">
@@ -55059,7 +55059,7 @@
       </c>
       <c r="AE477" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF477" t="inlineStr">
@@ -55179,7 +55179,7 @@
       </c>
       <c r="AE478" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF478" t="inlineStr">
@@ -55291,7 +55291,7 @@
       </c>
       <c r="AE479" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF479" t="inlineStr">
@@ -55403,7 +55403,7 @@
       </c>
       <c r="AE480" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF480" t="inlineStr">
@@ -55503,7 +55503,7 @@
       </c>
       <c r="AE481" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF481" t="inlineStr">
@@ -55619,7 +55619,7 @@
       </c>
       <c r="AE482" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF482" t="inlineStr">
@@ -55729,7 +55729,7 @@
       </c>
       <c r="AE483" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF483" t="inlineStr">
@@ -55841,7 +55841,7 @@
       </c>
       <c r="AE484" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF484" t="inlineStr">
@@ -55951,7 +55951,7 @@
       </c>
       <c r="AE485" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF485" t="inlineStr">
@@ -56063,7 +56063,7 @@
       </c>
       <c r="AE486" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF486" t="inlineStr">
@@ -56175,7 +56175,7 @@
       </c>
       <c r="AE487" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF487" t="inlineStr">
@@ -56275,7 +56275,7 @@
       </c>
       <c r="AE488" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF488" t="inlineStr">
@@ -56385,7 +56385,7 @@
       </c>
       <c r="AE489" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF489" t="inlineStr">
@@ -56497,7 +56497,7 @@
       </c>
       <c r="AE490" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF490" t="inlineStr">
@@ -56607,7 +56607,7 @@
       </c>
       <c r="AE491" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF491" t="inlineStr">
@@ -56717,7 +56717,7 @@
       </c>
       <c r="AE492" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF492" t="inlineStr">
@@ -56829,7 +56829,7 @@
       </c>
       <c r="AE493" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF493" t="inlineStr">
@@ -56939,7 +56939,7 @@
       </c>
       <c r="AE494" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF494" t="inlineStr">
@@ -57049,7 +57049,7 @@
       </c>
       <c r="AE495" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF495" t="inlineStr">
@@ -57159,7 +57159,7 @@
       </c>
       <c r="AE496" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF496" t="inlineStr">
@@ -57279,7 +57279,7 @@
       </c>
       <c r="AE497" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF497" t="inlineStr">
@@ -57403,7 +57403,7 @@
       </c>
       <c r="AE498" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:22</t>
+          <t>2026-10-01 15:39:44</t>
         </is>
       </c>
       <c r="AF498" t="inlineStr">
@@ -57513,7 +57513,7 @@
       </c>
       <c r="AE499" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF499" t="inlineStr">
@@ -57625,7 +57625,7 @@
       </c>
       <c r="AE500" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF500" t="inlineStr">
@@ -57735,7 +57735,7 @@
       </c>
       <c r="AE501" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF501" t="inlineStr">
@@ -57847,7 +57847,7 @@
       </c>
       <c r="AE502" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF502" t="inlineStr">
@@ -57959,7 +57959,7 @@
       </c>
       <c r="AE503" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF503" t="inlineStr">
@@ -58069,7 +58069,7 @@
       </c>
       <c r="AE504" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF504" t="inlineStr">
@@ -58179,7 +58179,7 @@
       </c>
       <c r="AE505" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF505" t="inlineStr">
@@ -58289,7 +58289,7 @@
       </c>
       <c r="AE506" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF506" t="inlineStr">
@@ -58399,7 +58399,7 @@
       </c>
       <c r="AE507" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF507" t="inlineStr">
@@ -58509,7 +58509,7 @@
       </c>
       <c r="AE508" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF508" t="inlineStr">
@@ -58619,7 +58619,7 @@
       </c>
       <c r="AE509" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF509" t="inlineStr">
@@ -58731,7 +58731,7 @@
       </c>
       <c r="AE510" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF510" t="inlineStr">
@@ -58843,7 +58843,7 @@
       </c>
       <c r="AE511" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF511" t="inlineStr">
@@ -58955,7 +58955,7 @@
       </c>
       <c r="AE512" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF512" t="inlineStr">
@@ -59065,7 +59065,7 @@
       </c>
       <c r="AE513" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF513" t="inlineStr">
@@ -59177,7 +59177,7 @@
       </c>
       <c r="AE514" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF514" t="inlineStr">
@@ -59277,7 +59277,7 @@
       </c>
       <c r="AE515" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF515" t="inlineStr">
@@ -59387,7 +59387,7 @@
       </c>
       <c r="AE516" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF516" t="inlineStr">
@@ -59487,7 +59487,7 @@
       </c>
       <c r="AE517" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF517" t="inlineStr">
@@ -59587,7 +59587,7 @@
       </c>
       <c r="AE518" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF518" t="inlineStr">
@@ -59699,7 +59699,7 @@
       </c>
       <c r="AE519" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF519" t="inlineStr">
@@ -59811,7 +59811,7 @@
       </c>
       <c r="AE520" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF520" t="inlineStr">
@@ -59923,7 +59923,7 @@
       </c>
       <c r="AE521" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF521" t="inlineStr">
@@ -60033,7 +60033,7 @@
       </c>
       <c r="AE522" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF522" t="inlineStr">
@@ -60143,7 +60143,7 @@
       </c>
       <c r="AE523" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF523" t="inlineStr">
@@ -60253,7 +60253,7 @@
       </c>
       <c r="AE524" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF524" t="inlineStr">
@@ -60365,7 +60365,7 @@
       </c>
       <c r="AE525" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF525" t="inlineStr">
@@ -60475,7 +60475,7 @@
       </c>
       <c r="AE526" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF526" t="inlineStr">
@@ -60585,7 +60585,7 @@
       </c>
       <c r="AE527" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF527" t="inlineStr">
@@ -60695,7 +60695,7 @@
       </c>
       <c r="AE528" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF528" t="inlineStr">
@@ -60805,7 +60805,7 @@
       </c>
       <c r="AE529" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF529" t="inlineStr">
@@ -60917,7 +60917,7 @@
       </c>
       <c r="AE530" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF530" t="inlineStr">
@@ -61029,7 +61029,7 @@
       </c>
       <c r="AE531" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF531" t="inlineStr">
@@ -61145,7 +61145,7 @@
       </c>
       <c r="AE532" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF532" t="inlineStr">
@@ -61273,7 +61273,7 @@
       </c>
       <c r="AE533" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF533" t="inlineStr">
@@ -61385,7 +61385,7 @@
       </c>
       <c r="AE534" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF534" t="inlineStr">
@@ -61495,7 +61495,7 @@
       </c>
       <c r="AE535" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF535" t="inlineStr">
@@ -61615,7 +61615,7 @@
       </c>
       <c r="AE536" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF536" t="inlineStr">
@@ -61725,7 +61725,7 @@
       </c>
       <c r="AE537" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF537" t="inlineStr">
@@ -61835,7 +61835,7 @@
       </c>
       <c r="AE538" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF538" t="inlineStr">
@@ -61945,7 +61945,7 @@
       </c>
       <c r="AE539" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF539" t="inlineStr">
@@ -62065,7 +62065,7 @@
       </c>
       <c r="AE540" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF540" t="inlineStr">
@@ -62181,7 +62181,7 @@
       </c>
       <c r="AE541" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF541" t="inlineStr">
@@ -62293,7 +62293,7 @@
       </c>
       <c r="AE542" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF542" t="inlineStr">
@@ -62413,7 +62413,7 @@
       </c>
       <c r="AE543" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF543" t="inlineStr">
@@ -62525,7 +62525,7 @@
       </c>
       <c r="AE544" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF544" t="inlineStr">
@@ -62625,7 +62625,7 @@
       </c>
       <c r="AE545" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF545" t="inlineStr">
@@ -62745,7 +62745,7 @@
       </c>
       <c r="AE546" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF546" t="inlineStr">
@@ -62855,7 +62855,7 @@
       </c>
       <c r="AE547" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF547" t="inlineStr">
@@ -62967,7 +62967,7 @@
       </c>
       <c r="AE548" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF548" t="inlineStr">
@@ -63083,7 +63083,7 @@
       </c>
       <c r="AE549" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF549" t="inlineStr">
@@ -63195,7 +63195,7 @@
       </c>
       <c r="AE550" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF550" t="inlineStr">
@@ -63307,7 +63307,7 @@
       </c>
       <c r="AE551" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF551" t="inlineStr">
@@ -63435,7 +63435,7 @@
       </c>
       <c r="AE552" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF552" t="inlineStr">
@@ -63545,7 +63545,7 @@
       </c>
       <c r="AE553" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF553" t="inlineStr">
@@ -63655,7 +63655,7 @@
       </c>
       <c r="AE554" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF554" t="inlineStr">
@@ -63765,7 +63765,7 @@
       </c>
       <c r="AE555" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF555" t="inlineStr">
@@ -63877,7 +63877,7 @@
       </c>
       <c r="AE556" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF556" t="inlineStr">
@@ -64005,7 +64005,7 @@
       </c>
       <c r="AE557" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF557" t="inlineStr">
@@ -64117,7 +64117,7 @@
       </c>
       <c r="AE558" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF558" t="inlineStr">
@@ -64229,7 +64229,7 @@
       </c>
       <c r="AE559" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF559" t="inlineStr">
@@ -64341,7 +64341,7 @@
       </c>
       <c r="AE560" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF560" t="inlineStr">
@@ -64441,7 +64441,7 @@
       </c>
       <c r="AE561" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF561" t="inlineStr">
@@ -64551,7 +64551,7 @@
       </c>
       <c r="AE562" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF562" t="inlineStr">
@@ -64661,7 +64661,7 @@
       </c>
       <c r="AE563" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF563" t="inlineStr">
@@ -64761,7 +64761,7 @@
       </c>
       <c r="AE564" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF564" t="inlineStr">
@@ -64871,7 +64871,7 @@
       </c>
       <c r="AE565" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF565" t="inlineStr">
@@ -64999,7 +64999,7 @@
       </c>
       <c r="AE566" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF566" t="inlineStr">
@@ -65109,7 +65109,7 @@
       </c>
       <c r="AE567" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF567" t="inlineStr">
@@ -65221,7 +65221,7 @@
       </c>
       <c r="AE568" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF568" t="inlineStr">
@@ -65331,7 +65331,7 @@
       </c>
       <c r="AE569" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF569" t="inlineStr">
@@ -65443,7 +65443,7 @@
       </c>
       <c r="AE570" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF570" t="inlineStr">
@@ -65553,7 +65553,7 @@
       </c>
       <c r="AE571" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF571" t="inlineStr">
@@ -65663,7 +65663,7 @@
       </c>
       <c r="AE572" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF572" t="inlineStr">
@@ -65763,7 +65763,7 @@
       </c>
       <c r="AE573" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF573" t="inlineStr">
@@ -65873,7 +65873,7 @@
       </c>
       <c r="AE574" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF574" t="inlineStr">
@@ -65985,7 +65985,7 @@
       </c>
       <c r="AE575" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF575" t="inlineStr">
@@ -66095,7 +66095,7 @@
       </c>
       <c r="AE576" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF576" t="inlineStr">
@@ -66205,7 +66205,7 @@
       </c>
       <c r="AE577" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF577" t="inlineStr">
@@ -66315,7 +66315,7 @@
       </c>
       <c r="AE578" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF578" t="inlineStr">
@@ -66425,7 +66425,7 @@
       </c>
       <c r="AE579" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF579" t="inlineStr">
@@ -66535,7 +66535,7 @@
       </c>
       <c r="AE580" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF580" t="inlineStr">
@@ -66645,7 +66645,7 @@
       </c>
       <c r="AE581" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF581" t="inlineStr">
@@ -66745,7 +66745,7 @@
       </c>
       <c r="AE582" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF582" t="inlineStr">
@@ -66855,7 +66855,7 @@
       </c>
       <c r="AE583" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF583" t="inlineStr">
@@ -66965,7 +66965,7 @@
       </c>
       <c r="AE584" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF584" t="inlineStr">
@@ -67077,7 +67077,7 @@
       </c>
       <c r="AE585" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF585" t="inlineStr">
@@ -67187,7 +67187,7 @@
       </c>
       <c r="AE586" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF586" t="inlineStr">
@@ -67299,7 +67299,7 @@
       </c>
       <c r="AE587" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF587" t="inlineStr">
@@ -67409,7 +67409,7 @@
       </c>
       <c r="AE588" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF588" t="inlineStr">
@@ -67519,7 +67519,7 @@
       </c>
       <c r="AE589" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF589" t="inlineStr">
@@ -67629,7 +67629,7 @@
       </c>
       <c r="AE590" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF590" t="inlineStr">
@@ -67739,7 +67739,7 @@
       </c>
       <c r="AE591" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF591" t="inlineStr">
@@ -67849,7 +67849,7 @@
       </c>
       <c r="AE592" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF592" t="inlineStr">
@@ -67961,7 +67961,7 @@
       </c>
       <c r="AE593" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF593" t="inlineStr">
@@ -68071,7 +68071,7 @@
       </c>
       <c r="AE594" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF594" t="inlineStr">
@@ -68183,7 +68183,7 @@
       </c>
       <c r="AE595" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF595" t="inlineStr">
@@ -68295,7 +68295,7 @@
       </c>
       <c r="AE596" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF596" t="inlineStr">
@@ -68405,7 +68405,7 @@
       </c>
       <c r="AE597" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF597" t="inlineStr">
@@ -68517,7 +68517,7 @@
       </c>
       <c r="AE598" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF598" t="inlineStr">
@@ -68629,7 +68629,7 @@
       </c>
       <c r="AE599" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF599" t="inlineStr">
@@ -68739,7 +68739,7 @@
       </c>
       <c r="AE600" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF600" t="inlineStr">
@@ -68849,7 +68849,7 @@
       </c>
       <c r="AE601" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF601" t="inlineStr">
@@ -68959,7 +68959,7 @@
       </c>
       <c r="AE602" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF602" t="inlineStr">
@@ -69069,7 +69069,7 @@
       </c>
       <c r="AE603" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF603" t="inlineStr">
@@ -69169,7 +69169,7 @@
       </c>
       <c r="AE604" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF604" t="inlineStr">
@@ -69281,7 +69281,7 @@
       </c>
       <c r="AE605" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF605" t="inlineStr">
@@ -69391,7 +69391,7 @@
       </c>
       <c r="AE606" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF606" t="inlineStr">
@@ -69501,7 +69501,7 @@
       </c>
       <c r="AE607" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF607" t="inlineStr">
@@ -69629,7 +69629,7 @@
       </c>
       <c r="AE608" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF608" t="inlineStr">
@@ -69741,7 +69741,7 @@
       </c>
       <c r="AE609" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF609" t="inlineStr">
@@ -69853,7 +69853,7 @@
       </c>
       <c r="AE610" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF610" t="inlineStr">
@@ -69981,7 +69981,7 @@
       </c>
       <c r="AE611" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF611" t="inlineStr">
@@ -70093,7 +70093,7 @@
       </c>
       <c r="AE612" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF612" t="inlineStr">
@@ -70221,7 +70221,7 @@
       </c>
       <c r="AE613" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF613" t="inlineStr">
@@ -70349,7 +70349,7 @@
       </c>
       <c r="AE614" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="AF614" t="inlineStr">
@@ -70461,7 +70461,7 @@
       </c>
       <c r="AE615" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF615" t="inlineStr">
@@ -70573,7 +70573,7 @@
       </c>
       <c r="AE616" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF616" t="inlineStr">
@@ -70683,7 +70683,7 @@
       </c>
       <c r="AE617" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF617" t="inlineStr">
@@ -70795,7 +70795,7 @@
       </c>
       <c r="AE618" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF618" t="inlineStr">
@@ -70905,7 +70905,7 @@
       </c>
       <c r="AE619" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF619" t="inlineStr">
@@ -71015,7 +71015,7 @@
       </c>
       <c r="AE620" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF620" t="inlineStr">
@@ -71127,7 +71127,7 @@
       </c>
       <c r="AE621" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF621" t="inlineStr">
@@ -71239,7 +71239,7 @@
       </c>
       <c r="AE622" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF622" t="inlineStr">
@@ -71351,7 +71351,7 @@
       </c>
       <c r="AE623" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF623" t="inlineStr">
@@ -71461,7 +71461,7 @@
       </c>
       <c r="AE624" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF624" t="inlineStr">
@@ -71571,7 +71571,7 @@
       </c>
       <c r="AE625" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF625" t="inlineStr">
@@ -71683,7 +71683,7 @@
       </c>
       <c r="AE626" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF626" t="inlineStr">
@@ -71795,7 +71795,7 @@
       </c>
       <c r="AE627" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF627" t="inlineStr">
@@ -71905,7 +71905,7 @@
       </c>
       <c r="AE628" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF628" t="inlineStr">
@@ -72017,7 +72017,7 @@
       </c>
       <c r="AE629" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF629" t="inlineStr">
@@ -72127,7 +72127,7 @@
       </c>
       <c r="AE630" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF630" t="inlineStr">
@@ -72227,7 +72227,7 @@
       </c>
       <c r="AE631" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF631" t="inlineStr">
@@ -72337,7 +72337,7 @@
       </c>
       <c r="AE632" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF632" t="inlineStr">
@@ -72449,7 +72449,7 @@
       </c>
       <c r="AE633" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF633" t="inlineStr">
@@ -72559,7 +72559,7 @@
       </c>
       <c r="AE634" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF634" t="inlineStr">
@@ -72671,7 +72671,7 @@
       </c>
       <c r="AE635" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF635" t="inlineStr">
@@ -72781,7 +72781,7 @@
       </c>
       <c r="AE636" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF636" t="inlineStr">
@@ -72891,7 +72891,7 @@
       </c>
       <c r="AE637" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF637" t="inlineStr">
@@ -73001,7 +73001,7 @@
       </c>
       <c r="AE638" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF638" t="inlineStr">
@@ -73111,7 +73111,7 @@
       </c>
       <c r="AE639" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF639" t="inlineStr">
@@ -73221,7 +73221,7 @@
       </c>
       <c r="AE640" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF640" t="inlineStr">
@@ -73333,7 +73333,7 @@
       </c>
       <c r="AE641" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF641" t="inlineStr">
@@ -73443,7 +73443,7 @@
       </c>
       <c r="AE642" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF642" t="inlineStr">
@@ -73553,7 +73553,7 @@
       </c>
       <c r="AE643" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF643" t="inlineStr">
@@ -73663,7 +73663,7 @@
       </c>
       <c r="AE644" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF644" t="inlineStr">
@@ -73775,7 +73775,7 @@
       </c>
       <c r="AE645" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF645" t="inlineStr">
@@ -73885,7 +73885,7 @@
       </c>
       <c r="AE646" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF646" t="inlineStr">
@@ -73997,7 +73997,7 @@
       </c>
       <c r="AE647" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF647" t="inlineStr">
@@ -74109,7 +74109,7 @@
       </c>
       <c r="AE648" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF648" t="inlineStr">
@@ -74209,7 +74209,7 @@
       </c>
       <c r="AE649" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF649" t="inlineStr">
@@ -74319,7 +74319,7 @@
       </c>
       <c r="AE650" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF650" t="inlineStr">
@@ -74431,7 +74431,7 @@
       </c>
       <c r="AE651" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF651" t="inlineStr">
@@ -74543,7 +74543,7 @@
       </c>
       <c r="AE652" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF652" t="inlineStr">
@@ -74655,7 +74655,7 @@
       </c>
       <c r="AE653" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF653" t="inlineStr">
@@ -74767,7 +74767,7 @@
       </c>
       <c r="AE654" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF654" t="inlineStr">
@@ -74877,7 +74877,7 @@
       </c>
       <c r="AE655" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF655" t="inlineStr">
@@ -74987,7 +74987,7 @@
       </c>
       <c r="AE656" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF656" t="inlineStr">
@@ -75099,7 +75099,7 @@
       </c>
       <c r="AE657" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF657" t="inlineStr">
@@ -75209,7 +75209,7 @@
       </c>
       <c r="AE658" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF658" t="inlineStr">
@@ -75321,7 +75321,7 @@
       </c>
       <c r="AE659" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF659" t="inlineStr">
@@ -75421,7 +75421,7 @@
       </c>
       <c r="AE660" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF660" t="inlineStr">
@@ -75531,7 +75531,7 @@
       </c>
       <c r="AE661" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF661" t="inlineStr">
@@ -75643,7 +75643,7 @@
       </c>
       <c r="AE662" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF662" t="inlineStr">
@@ -75753,7 +75753,7 @@
       <c r="AD663" t="inlineStr"/>
       <c r="AE663" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:35</t>
+          <t>2026-10-01 15:39:59</t>
         </is>
       </c>
       <c r="AF663" t="inlineStr">
@@ -75865,7 +75865,7 @@
       </c>
       <c r="AE664" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF664" t="inlineStr">
@@ -75977,7 +75977,7 @@
       </c>
       <c r="AE665" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF665" t="inlineStr">
@@ -76087,7 +76087,7 @@
       </c>
       <c r="AE666" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF666" t="inlineStr">
@@ -76199,7 +76199,7 @@
       </c>
       <c r="AE667" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF667" t="inlineStr">
@@ -76299,7 +76299,7 @@
       </c>
       <c r="AE668" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF668" t="inlineStr">
@@ -76399,7 +76399,7 @@
       </c>
       <c r="AE669" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF669" t="inlineStr">
@@ -76499,7 +76499,7 @@
       </c>
       <c r="AE670" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF670" t="inlineStr">
@@ -76611,7 +76611,7 @@
       </c>
       <c r="AE671" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF671" t="inlineStr">
@@ -76711,7 +76711,7 @@
       </c>
       <c r="AE672" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF672" t="inlineStr">
@@ -76821,7 +76821,7 @@
       </c>
       <c r="AE673" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF673" t="inlineStr">
@@ -76921,7 +76921,7 @@
       </c>
       <c r="AE674" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF674" t="inlineStr">
@@ -77033,7 +77033,7 @@
       </c>
       <c r="AE675" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF675" t="inlineStr">
@@ -77145,7 +77145,7 @@
       </c>
       <c r="AE676" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF676" t="inlineStr">
@@ -77257,7 +77257,7 @@
       </c>
       <c r="AE677" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF677" t="inlineStr">
@@ -77369,7 +77369,7 @@
       </c>
       <c r="AE678" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF678" t="inlineStr">
@@ -77469,7 +77469,7 @@
       </c>
       <c r="AE679" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF679" t="inlineStr">
@@ -77581,7 +77581,7 @@
       </c>
       <c r="AE680" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF680" t="inlineStr">
@@ -77691,7 +77691,7 @@
       </c>
       <c r="AE681" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF681" t="inlineStr">
@@ -77803,7 +77803,7 @@
       </c>
       <c r="AE682" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF682" t="inlineStr">
@@ -77903,7 +77903,7 @@
       </c>
       <c r="AE683" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF683" t="inlineStr">
@@ -78003,7 +78003,7 @@
       </c>
       <c r="AE684" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF684" t="inlineStr">
@@ -78103,7 +78103,7 @@
       </c>
       <c r="AE685" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF685" t="inlineStr">
@@ -78203,7 +78203,7 @@
       </c>
       <c r="AE686" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF686" t="inlineStr">
@@ -78315,7 +78315,7 @@
       </c>
       <c r="AE687" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF687" t="inlineStr">
@@ -78427,7 +78427,7 @@
       </c>
       <c r="AE688" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF688" t="inlineStr">
@@ -78527,7 +78527,7 @@
       </c>
       <c r="AE689" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF689" t="inlineStr">
@@ -78637,7 +78637,7 @@
       </c>
       <c r="AE690" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF690" t="inlineStr">
@@ -78749,7 +78749,7 @@
       </c>
       <c r="AE691" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF691" t="inlineStr">
@@ -78861,7 +78861,7 @@
       </c>
       <c r="AE692" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF692" t="inlineStr">
@@ -78973,7 +78973,7 @@
       </c>
       <c r="AE693" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF693" t="inlineStr">
@@ -79085,7 +79085,7 @@
       </c>
       <c r="AE694" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF694" t="inlineStr">
@@ -79197,7 +79197,7 @@
       </c>
       <c r="AE695" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF695" t="inlineStr">
@@ -79309,7 +79309,7 @@
       </c>
       <c r="AE696" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF696" t="inlineStr">
@@ -79421,7 +79421,7 @@
       </c>
       <c r="AE697" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF697" t="inlineStr">
@@ -79521,7 +79521,7 @@
       </c>
       <c r="AE698" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF698" t="inlineStr">
@@ -79621,7 +79621,7 @@
       </c>
       <c r="AE699" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF699" t="inlineStr">
@@ -79733,7 +79733,7 @@
       </c>
       <c r="AE700" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:03</t>
+          <t>2026-10-01 15:39:27</t>
         </is>
       </c>
       <c r="AF700" t="inlineStr">
@@ -79833,7 +79833,7 @@
       </c>
       <c r="AE701" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF701" t="inlineStr">
@@ -79933,7 +79933,7 @@
       </c>
       <c r="AE702" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF702" t="inlineStr">
@@ -80033,7 +80033,7 @@
       </c>
       <c r="AE703" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF703" t="inlineStr">
@@ -80143,7 +80143,7 @@
       </c>
       <c r="AE704" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF704" t="inlineStr">
@@ -80243,7 +80243,7 @@
       </c>
       <c r="AE705" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF705" t="inlineStr">
@@ -80353,7 +80353,7 @@
       </c>
       <c r="AE706" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF706" t="inlineStr">
@@ -80435,7 +80435,7 @@
       <c r="AD707" t="inlineStr"/>
       <c r="AE707" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF707" t="inlineStr">
@@ -80517,7 +80517,7 @@
       <c r="AD708" t="inlineStr"/>
       <c r="AE708" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF708" t="inlineStr">
@@ -80599,7 +80599,7 @@
       <c r="AD709" t="inlineStr"/>
       <c r="AE709" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF709" t="inlineStr">
@@ -80681,7 +80681,7 @@
       <c r="AD710" t="inlineStr"/>
       <c r="AE710" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="AF710" t="inlineStr">
